--- a/docs/bank-onto-bench-v2.xlsx
+++ b/docs/bank-onto-bench-v2.xlsx
@@ -13873,7 +13873,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>경남은행 '장기카드대출(장기카드대출(카드론))'은(는) 영업점 경로로 가입할 수 있는가?</t>
+          <t>경남은행 '장기카드대출(카드론)'은(는) 영업점 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>광주은행 '장기카드대출(장기카드대출(카드론))'은(는) 영업점 경로로 가입할 수 있는가?</t>
+          <t>광주은행 '장기카드대출(카드론)'은(는) 영업점 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>광주은행 '장기카드대출(장기카드대출(카드론))'은(는) 스마트폰 경로로 가입할 수 있는가?</t>
+          <t>광주은행 '장기카드대출(카드론)'은(는) 스마트폰 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>농협은행주식회사 '장기카드대출(장기카드대출(카드론))'은(는) 영업점 경로로 가입할 수 있는가?</t>
+          <t>농협은행주식회사 '장기카드대출(카드론)'은(는) 영업점 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -15033,7 +15033,7 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>부산은행 '장기카드대출(장기카드대출(카드론))'은(는) 영업점 경로로 가입할 수 있는가?</t>
+          <t>부산은행 '장기카드대출(카드론)'은(는) 영업점 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>부산은행 '장기카드대출(장기카드대출(카드론))'은(는) 스마트폰 경로로 가입할 수 있는가?</t>
+          <t>부산은행 '장기카드대출(카드론)'은(는) 스마트폰 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>아이엠뱅크 '장기카드대출(장기카드대출(카드론))'은(는) 스마트폰 경로로 가입할 수 있는가?</t>
+          <t>아이엠뱅크 '장기카드대출(카드론)'은(는) 스마트폰 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>아이엠뱅크 '장기카드대출(장기카드대출(카드론))'은(는) 영업점 경로로 가입할 수 있는가?</t>
+          <t>아이엠뱅크 '장기카드대출(카드론)'은(는) 영업점 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>전북은행 '장기카드대출(장기카드대출(카드론))'은(는) 영업점 경로로 가입할 수 있는가?</t>
+          <t>전북은행 '장기카드대출(카드론)'은(는) 영업점 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -16483,7 +16483,7 @@
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>전북은행 '장기카드대출(장기카드대출(카드론))'은(는) 인터넷 경로로 가입할 수 있는가?</t>
+          <t>전북은행 '장기카드대출(카드론)'은(는) 인터넷 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>중소기업은행 '장기카드대출(장기카드대출(카드론))'은(는) 영업점 경로로 가입할 수 있는가?</t>
+          <t>중소기업은행 '장기카드대출(카드론)'은(는) 영업점 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
@@ -18459,7 +18459,7 @@
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>한국씨티은행 '장기카드대출(장기카드대출(카드론))'은(는) 인터넷 경로로 가입할 수 있는가?</t>
+          <t>한국씨티은행 '장기카드대출(카드론)'은(는) 인터넷 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
@@ -18517,7 +18517,7 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>한국씨티은행 '장기카드대출(장기카드대출(카드론))'은(는) 영업점 경로로 가입할 수 있는가?</t>
+          <t>한국씨티은행 '장기카드대출(카드론)'은(는) 영업점 경로로 가입할 수 있는가?</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
@@ -36857,7 +36857,7 @@
       </c>
       <c r="F612" s="2" t="inlineStr">
         <is>
-          <t>경남은행 '장기카드대출(장기카드대출(카드론))'의 공시된 평균 대출금리는 연 몇 %인가?</t>
+          <t>경남은행 '장기카드대출(카드론)'의 공시된 평균 대출금리는 연 몇 %인가?</t>
         </is>
       </c>
       <c r="G612" s="2" t="inlineStr">
@@ -37043,7 +37043,7 @@
       </c>
       <c r="F615" s="2" t="inlineStr">
         <is>
-          <t>광주은행 '장기카드대출(장기카드대출(카드론))'의 공시된 평균 대출금리는 연 몇 %인가?</t>
+          <t>광주은행 '장기카드대출(카드론)'의 공시된 평균 대출금리는 연 몇 %인가?</t>
         </is>
       </c>
       <c r="G615" s="2" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="F620" s="2" t="inlineStr">
         <is>
-          <t>농협은행주식회사 '장기카드대출(장기카드대출(카드론))'의 공시된 평균 대출금리는 연 몇 %인가?</t>
+          <t>농협은행주식회사 '장기카드대출(카드론)'의 공시된 평균 대출금리는 연 몇 %인가?</t>
         </is>
       </c>
       <c r="G620" s="2" t="inlineStr">
@@ -37539,7 +37539,7 @@
       </c>
       <c r="F623" s="2" t="inlineStr">
         <is>
-          <t>부산은행 '장기카드대출(장기카드대출(카드론))'의 공시된 평균 대출금리는 연 몇 %인가?</t>
+          <t>부산은행 '장기카드대출(카드론)'의 공시된 평균 대출금리는 연 몇 %인가?</t>
         </is>
       </c>
       <c r="G623" s="2" t="inlineStr">
@@ -37973,7 +37973,7 @@
       </c>
       <c r="F630" s="2" t="inlineStr">
         <is>
-          <t>아이엠뱅크 '장기카드대출(장기카드대출(카드론))'의 공시된 평균 대출금리는 연 몇 %인가?</t>
+          <t>아이엠뱅크 '장기카드대출(카드론)'의 공시된 평균 대출금리는 연 몇 %인가?</t>
         </is>
       </c>
       <c r="G630" s="2" t="inlineStr">
@@ -38283,7 +38283,7 @@
       </c>
       <c r="F635" s="2" t="inlineStr">
         <is>
-          <t>전북은행 '장기카드대출(장기카드대출(카드론))'의 공시된 평균 대출금리는 연 몇 %인가?</t>
+          <t>전북은행 '장기카드대출(카드론)'의 공시된 평균 대출금리는 연 몇 %인가?</t>
         </is>
       </c>
       <c r="G635" s="2" t="inlineStr">
@@ -38833,7 +38833,7 @@
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>경남은행 '장기카드대출(장기카드대출(카드론))'의 공시된 최고 한도 금액은 얼마인가?</t>
+          <t>경남은행 '장기카드대출(카드론)'의 공시된 최고 한도 금액은 얼마인가?</t>
         </is>
       </c>
       <c r="G644" s="2" t="inlineStr">
@@ -39007,7 +39007,7 @@
       </c>
       <c r="F647" s="2" t="inlineStr">
         <is>
-          <t>광주은행 '장기카드대출(장기카드대출(카드론))'의 공시된 최고 한도 금액은 얼마인가?</t>
+          <t>광주은행 '장기카드대출(카드론)'의 공시된 최고 한도 금액은 얼마인가?</t>
         </is>
       </c>
       <c r="G647" s="2" t="inlineStr">
@@ -39297,7 +39297,7 @@
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>농협은행주식회사 '장기카드대출(장기카드대출(카드론))'의 공시된 최고 한도 금액은 얼마인가?</t>
+          <t>농협은행주식회사 '장기카드대출(카드론)'의 공시된 최고 한도 금액은 얼마인가?</t>
         </is>
       </c>
       <c r="G652" s="2" t="inlineStr">
@@ -39471,7 +39471,7 @@
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>부산은행 '장기카드대출(장기카드대출(카드론))'의 공시된 최고 한도 금액은 얼마인가?</t>
+          <t>부산은행 '장기카드대출(카드론)'의 공시된 최고 한도 금액은 얼마인가?</t>
         </is>
       </c>
       <c r="G655" s="2" t="inlineStr">
@@ -39877,7 +39877,7 @@
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>아이엠뱅크 '장기카드대출(장기카드대출(카드론))'의 공시된 최고 한도 금액은 얼마인가?</t>
+          <t>아이엠뱅크 '장기카드대출(카드론)'의 공시된 최고 한도 금액은 얼마인가?</t>
         </is>
       </c>
       <c r="G662" s="2" t="inlineStr">
@@ -40167,7 +40167,7 @@
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>전북은행 '장기카드대출(장기카드대출(카드론))'의 공시된 최고 한도 금액은 얼마인가?</t>
+          <t>전북은행 '장기카드대출(카드론)'의 공시된 최고 한도 금액은 얼마인가?</t>
         </is>
       </c>
       <c r="G667" s="2" t="inlineStr">
@@ -40807,7 +40807,7 @@
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>중소기업은행 '장기카드대출(장기카드대출(카드론))'의 공시된 최고 한도 금액은 얼마인가?</t>
+          <t>중소기업은행 '장기카드대출(카드론)'의 공시된 최고 한도 금액은 얼마인가?</t>
         </is>
       </c>
       <c r="G678" s="2" t="inlineStr">
@@ -41213,7 +41213,7 @@
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
-          <t>한국씨티은행 '장기카드대출(장기카드대출(카드론))'의 공시된 최고 한도 금액은 얼마인가?</t>
+          <t>한국씨티은행 '장기카드대출(카드론)'의 공시된 최고 한도 금액은 얼마인가?</t>
         </is>
       </c>
       <c r="G685" s="2" t="inlineStr">
